--- a/Tools/Luban/DataTables/Datas/法术定义_SpellDefinition.xlsx
+++ b/Tools/Luban/DataTables/Datas/法术定义_SpellDefinition.xlsx
@@ -374,7 +374,7 @@
         <x:v>SPELL_FIREBALL_NAME</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Spell/Icon/Fireball</x:v>
+        <x:v>icon_spellFireball</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
@@ -392,7 +392,7 @@
         <x:v>SPELL_CHAIN_LIGHTNING_NAME</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>Spell/Icon/ChainLightning</x:v>
+        <x:v>icon_spellChainLightning</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
@@ -410,7 +410,7 @@
         <x:v>SPELL_FROST_RING_NAME</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>Spell/Icon/FrostRing</x:v>
+        <x:v>icon_spellIceRing</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -428,7 +428,7 @@
         <x:v>SPELL_SHIELD_NAME</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Spell/Icon/Shield</x:v>
+        <x:v>icon_spellRuneShield</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
